--- a/03.GraphModels/weight_nx(toy).xlsx
+++ b/03.GraphModels/weight_nx(toy).xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26731"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26827"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\buildbr\big-cities-transport\04.Disparity\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\buildbr\big-cities-transport\03.GraphModels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{416C3836-D447-4719-A632-9AE08F5BBB07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B89F507-2CF3-4C93-B478-817702C0CA23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22932" yWindow="-5304" windowWidth="13176" windowHeight="22536" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Nodes" sheetId="3" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="47">
   <si>
     <t>Degree</t>
   </si>
@@ -53,42 +53,6 @@
   </si>
   <si>
     <t>Target</t>
-  </si>
-  <si>
-    <t>0.13374325688138586</t>
-  </si>
-  <si>
-    <t>0.08350670495869392</t>
-  </si>
-  <si>
-    <t>0.15188518266648784</t>
-  </si>
-  <si>
-    <t>0.08299285111505125</t>
-  </si>
-  <si>
-    <t>0.1671970173871082</t>
-  </si>
-  <si>
-    <t>0.10059917468322445</t>
-  </si>
-  <si>
-    <t>0.3010903804000408</t>
-  </si>
-  <si>
-    <t>0.17099176120369305</t>
-  </si>
-  <si>
-    <t>0.0816813518425639</t>
-  </si>
-  <si>
-    <t>0.32557907697436433</t>
-  </si>
-  <si>
-    <t>0.10191074340008159</t>
-  </si>
-  <si>
-    <t>0.10191074340008163</t>
   </si>
   <si>
     <t>Node</t>
@@ -657,28 +621,28 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
       </c>
       <c r="C1" t="s">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="D1" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="E1" t="s">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="F1" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="G1" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="H1" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
@@ -689,22 +653,22 @@
         <v>2</v>
       </c>
       <c r="C2" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="D2" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="F2" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="G2" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="H2" t="s">
-        <v>27</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
@@ -715,22 +679,22 @@
         <v>4</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
@@ -741,22 +705,22 @@
         <v>8</v>
       </c>
       <c r="C4" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="D4" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="F4" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="G4" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="H4" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
@@ -767,22 +731,22 @@
         <v>4</v>
       </c>
       <c r="C5" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="D5" t="s">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="F5" t="s">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="G5" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="H5" t="s">
-        <v>45</v>
+        <v>33</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
@@ -793,22 +757,22 @@
         <v>2</v>
       </c>
       <c r="C6" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="D6" t="s">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="F6" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="G6" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="H6" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
@@ -819,22 +783,22 @@
         <v>4</v>
       </c>
       <c r="C7" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="D7" t="s">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="F7" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="G7" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="H7" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="J7" s="4"/>
     </row>
@@ -860,7 +824,7 @@
         <v>2</v>
       </c>
       <c r="C1" t="s">
-        <v>58</v>
+        <v>46</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
@@ -870,8 +834,8 @@
       <c r="B2">
         <v>213</v>
       </c>
-      <c r="C2" t="s">
-        <v>3</v>
+      <c r="C2">
+        <v>0.63911286921485921</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -881,8 +845,8 @@
       <c r="B3">
         <v>183</v>
       </c>
-      <c r="C3" t="s">
-        <v>4</v>
+      <c r="C3">
+        <v>0.196934411301812</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
@@ -892,8 +856,8 @@
       <c r="B4">
         <v>231</v>
       </c>
-      <c r="C4" t="s">
-        <v>5</v>
+      <c r="C4">
+        <v>0.19227987334524232</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
@@ -903,8 +867,8 @@
       <c r="B5">
         <v>213</v>
       </c>
-      <c r="C5" t="s">
-        <v>6</v>
+      <c r="C5">
+        <v>0.60154995179880622</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
@@ -914,8 +878,8 @@
       <c r="B6">
         <v>46</v>
       </c>
-      <c r="C6" t="s">
-        <v>7</v>
+      <c r="C6">
+        <v>0.53974738525744292</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
@@ -925,8 +889,8 @@
       <c r="B7">
         <v>0</v>
       </c>
-      <c r="C7" t="s">
-        <v>8</v>
+      <c r="C7">
+        <v>0.59756352173538707</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
@@ -936,8 +900,8 @@
       <c r="B8">
         <v>92</v>
       </c>
-      <c r="C8" t="s">
-        <v>9</v>
+      <c r="C8">
+        <v>0.41217941440541717</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
@@ -947,8 +911,8 @@
       <c r="B9">
         <v>231</v>
       </c>
-      <c r="C9" t="s">
-        <v>10</v>
+      <c r="C9">
+        <v>9.8580800116841116E-2</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
@@ -958,8 +922,8 @@
       <c r="B10">
         <v>231</v>
       </c>
-      <c r="C10" t="s">
-        <v>11</v>
+      <c r="C10">
+        <v>0.55654619556922191</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
@@ -969,8 +933,8 @@
       <c r="B11">
         <v>231</v>
       </c>
-      <c r="C11" t="s">
-        <v>12</v>
+      <c r="C11">
+        <v>0.15884716553963008</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
@@ -980,8 +944,8 @@
       <c r="B12">
         <v>46</v>
       </c>
-      <c r="C12" t="s">
-        <v>13</v>
+      <c r="C12">
+        <v>0.53022929334032753</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
@@ -991,8 +955,8 @@
       <c r="B13">
         <v>0</v>
       </c>
-      <c r="C13" t="s">
-        <v>14</v>
+      <c r="C13">
+        <v>0.76238795054320962</v>
       </c>
     </row>
   </sheetData>
